--- a/Dokumentaion/Testplanung_vorlage.xlsx
+++ b/Dokumentaion/Testplanung_vorlage.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/Dokumentaion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{792F2CBC-5F3F-1742-83E1-B73181E8C215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{792439EC-D7CC-B243-A3D1-9A9631E7BBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="660" yWindow="1980" windowWidth="28040" windowHeight="17400" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
+    <workbookView xWindow="5080" yWindow="560" windowWidth="25460" windowHeight="17500" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191028"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="32">
   <si>
     <t>Analyse</t>
   </si>
@@ -59,74 +60,93 @@
     <t>Einstufung</t>
   </si>
   <si>
-    <t>Es werden 4 von 5 falschen Einträgen erkannt</t>
-  </si>
-  <si>
     <t>Critical</t>
   </si>
   <si>
     <t>Major</t>
   </si>
   <si>
-    <t>Hauptfehler
---&gt; Bereinigt bis Datum</t>
-  </si>
-  <si>
     <t>Minor</t>
   </si>
   <si>
-    <t>Nebenfehler
---&gt; werden manchmal behoben</t>
-  </si>
-  <si>
-    <t>Es weden 25 Reservierungsanfragen erzeugt . Davon sind5 nicht vollständig ausgefüllt</t>
-  </si>
-  <si>
-    <t>Es werden 5/5 falsche
-reserv anfragen erkannt</t>
-  </si>
-  <si>
-    <t>die reservierung wird gebucht</t>
-  </si>
-  <si>
-    <t>minor</t>
-  </si>
-  <si>
-    <t>platz 10 ist bereits reserviert. Es wird eine anfrage gestellt ob platz 10 noch frei ist. (es wird mehrmals wiederholt mit vers plätzen)</t>
-  </si>
-  <si>
-    <t>Die anfrage wird ina llen fällen  abgewiesen</t>
-  </si>
-  <si>
-    <t>Jeder Benutzer muss eindeutige ID, Namen und Rolle haben</t>
-  </si>
-  <si>
-    <t>Projekt muss ID, Name, Kunde, Projektleiter und Kernanforderungen enthalten</t>
-  </si>
-  <si>
-    <t>Projekt wird automatisch in der Liste des Projektleiters gespeichert</t>
-  </si>
-  <si>
-    <t>Benutzer (PL oder Mitarbeiter) kann Information erstellen</t>
-  </si>
-  <si>
-    <t>Information wird dem Projekt zugeordnet</t>
-  </si>
-  <si>
-    <t>PL und Mitarbeiter dürfen kommentieren</t>
-  </si>
-  <si>
-    <t>PL und Mitarbeiter können nach Tags suchen</t>
-  </si>
-  <si>
-    <t>*PL und Mitarbeiter können Projektinformationen einsehen</t>
+    <t>PM darf kein Projekt erstellen</t>
+  </si>
+  <si>
+    <t>Benutzer können die Informationen nach Tags durchsuchen.</t>
+  </si>
+  <si>
+    <t>Benutzer können die Information kommentieren. </t>
+  </si>
+  <si>
+    <t>Benutzer müssen die Informationen  mit 1 - 3 Tags versehen</t>
+  </si>
+  <si>
+    <t>PL kann ein Projekt erstellen.</t>
+  </si>
+  <si>
+    <t>Benutzer können eine Information erstellen.</t>
+  </si>
+  <si>
+    <t>Ein Projekt wird erstellt 
+Es wird gespeichert 
+Der Projektleiter ist korrekt gesetzt</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>Ein Projektleiter erstellt  ein Projekt</t>
+  </si>
+  <si>
+    <t>Ein Mitarbeiter erstellt ein Projekt</t>
+  </si>
+  <si>
+    <t>Kein neues Projekt darf hinzugefügt werden</t>
+  </si>
+  <si>
+    <t>eine Information wird erstellt 
+Information wird dem Projekt hinzugefügt
+Tags sind korrekt gesetzt</t>
+  </si>
+  <si>
+    <t>Ein Benuter erstellt eine Information</t>
+  </si>
+  <si>
+    <t>Ein Benutzer kommentiert die Information</t>
+  </si>
+  <si>
+    <t>Genau 1 neuer Kommentar wurde hinzugefügt 
+Der Text stimmt
+Der Autor ist korrekt gesetzt, Kommentar ist in der Liste der Kommentare</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ein Benutzer sucht nach Informationen mit </t>
+  </si>
+  <si>
+    <t>Suche nach einem Tag innerhalb eines Projekts funktioniert
+Nur die Informationen mit dem gesuchten Tag werden zurückgegeben</t>
+  </si>
+  <si>
+    <t>4 Tags werden erstellt</t>
+  </si>
+  <si>
+    <t>Methode wirft eine Exception, die Information nicht dem Projekt hinzugefügt</t>
+  </si>
+  <si>
+    <t>Kritische Abweichung --&gt; Abnahme gescheitert</t>
+  </si>
+  <si>
+    <t>Hauptfehler, --&gt; Bereinigt bis Datum</t>
+  </si>
+  <si>
+    <t>Nebenfehler --&gt; werden manchmal behoben</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -148,6 +168,32 @@
       <color rgb="FFFF0000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Helvetica"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -177,7 +223,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -222,11 +268,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -238,13 +297,7 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -254,7 +307,36 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -589,26 +671,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442EAB51-1B04-4EB1-9301-8BEA8EB4D474}">
-  <dimension ref="A2:E15"/>
+  <dimension ref="A2:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="55.6640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="33.33203125" style="1" customWidth="1"/>
-    <col min="3" max="3" width="21" style="1" customWidth="1"/>
+    <col min="2" max="2" width="27.6640625" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.33203125" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.1640625" style="1" customWidth="1"/>
     <col min="5" max="5" width="21.1640625" style="1" customWidth="1"/>
     <col min="6" max="16384" width="10.6640625" style="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11" t="s">
+      <c r="C2" s="8"/>
+      <c r="D2" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="12"/>
+      <c r="E2" s="10"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -620,152 +702,188 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="7" t="s">
         <v>5</v>
       </c>
       <c r="E3" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4" s="13"/>
-      <c r="B4" s="2"/>
-      <c r="C4" s="2"/>
-      <c r="D4" s="2"/>
-      <c r="E4" s="2"/>
-    </row>
-    <row r="5" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A5" s="13" t="s">
+    <row r="4" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="C5" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:5" ht="48" x14ac:dyDescent="0.2">
+      <c r="A6" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="5"/>
+    </row>
+    <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
+      <c r="A7" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D5" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="5"/>
+    </row>
+    <row r="8" spans="1:5" ht="80" x14ac:dyDescent="0.2">
+      <c r="A8" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="5"/>
+    </row>
+    <row r="9" spans="1:5" ht="64" x14ac:dyDescent="0.2">
+      <c r="A9" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="5"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D10" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="E5" s="5" t="s">
+      <c r="E10" s="21" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D11" s="18"/>
+      <c r="E11" s="22"/>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D12" s="19" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="49" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="E6" s="5" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="B7" s="3"/>
-      <c r="C7" s="3"/>
-      <c r="D7" s="4"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="3"/>
-      <c r="C8" s="3"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="13" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3"/>
-      <c r="C9" s="3"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="13" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="3"/>
-      <c r="C10" s="3"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="13" t="s">
-        <v>26</v>
-      </c>
-      <c r="B12" s="3"/>
-      <c r="C12" s="3"/>
-      <c r="D12" s="4"/>
-      <c r="E12" s="5"/>
+      <c r="E12" s="23" t="s">
+        <v>30</v>
+      </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="9"/>
-      <c r="E13" s="6" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="D14" s="6" t="s">
+      <c r="D13" s="19"/>
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D14" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="D15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>12</v>
-      </c>
+      <c r="E14" s="25" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="D15" s="20"/>
+      <c r="E15" s="26"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E16" s="15"/>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="E17" s="15"/>
+    </row>
+    <row r="18" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="E18" s="16"/>
+    </row>
+    <row r="19" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="E19" s="16"/>
+    </row>
+    <row r="20" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C20" s="13"/>
+    </row>
+    <row r="21" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C21" s="13"/>
+    </row>
+    <row r="22" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C22" s="14"/>
+    </row>
+    <row r="23" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C23" s="14"/>
+    </row>
+    <row r="24" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C24" s="17"/>
+    </row>
+    <row r="25" spans="3:5" x14ac:dyDescent="0.2">
+      <c r="C25" s="17"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="10">
+    <mergeCell ref="E18:E19"/>
+    <mergeCell ref="D14:D15"/>
+    <mergeCell ref="E10:E11"/>
+    <mergeCell ref="E12:E13"/>
+    <mergeCell ref="E14:E15"/>
     <mergeCell ref="B2:C2"/>
     <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E16:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010047E1B4110D667F4BADC525742D5EE2E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d4242f0faca51ba845790f185672872f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b989ebd0-cfbd-4347-a61d-09d2ec87900e" xmlns:ns3="26aae414-ca61-41d7-9f0a-f5a0a53751b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d27d03a123c6c0eefdfdcad7d866e60f" ns2:_="" ns3:_="">
     <xsd:import namespace="b989ebd0-cfbd-4347-a61d-09d2ec87900e"/>
@@ -960,6 +1078,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -972,14 +1099,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00B6F33-1652-4D35-BCCC-71D64DD37397}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -998,6 +1117,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD56C91E-EFEF-46AC-A071-D7F993F6AB1F}">
   <ds:schemaRefs>

--- a/Dokumentaion/Testplanung_vorlage.xlsx
+++ b/Dokumentaion/Testplanung_vorlage.xlsx
@@ -1,22 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10222"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10302"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/salome/Desktop/AL/Projektarbeit_Verwaltungssystem/Dokumentaion/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:2001_{792439EC-D7CC-B243-A3D1-9A9631E7BBD1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{410698A8-6BB5-1F4A-903F-92D65E2E4AA9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="560" windowWidth="25460" windowHeight="17500" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
+    <workbookView xWindow="160" yWindow="660" windowWidth="28480" windowHeight="17200" xr2:uid="{9C349EA5-900C-4B8E-A30C-FDD5A403C362}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">Tabelle1!$A$1:$E$15</definedName>
+  </definedNames>
   <calcPr calcId="191028"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -250,15 +252,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -281,11 +274,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="27">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
@@ -297,46 +301,40 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -671,6 +669,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{442EAB51-1B04-4EB1-9301-8BEA8EB4D474}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A2:E25"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
@@ -683,14 +684,15 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="B2" s="8" t="s">
+      <c r="A2" s="2"/>
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="D2" s="9" t="s">
+      <c r="C2" s="17"/>
+      <c r="D2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="10"/>
+      <c r="E2" s="23"/>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
@@ -702,15 +704,15 @@
       <c r="C3" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="2" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="65" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="11" t="s">
+      <c r="A4" s="24" t="s">
         <v>14</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -725,7 +727,7 @@
       <c r="E4" s="5"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="11" t="s">
+      <c r="A5" s="24" t="s">
         <v>10</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -740,7 +742,7 @@
       <c r="E5" s="5"/>
     </row>
     <row r="6" spans="1:5" ht="48" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
+      <c r="A6" s="24" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="3" t="s">
@@ -755,13 +757,13 @@
       <c r="E6" s="5"/>
     </row>
     <row r="7" spans="1:5" ht="32" x14ac:dyDescent="0.2">
-      <c r="A7" s="11" t="s">
+      <c r="A7" s="24" t="s">
         <v>13</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="C7" s="12" t="s">
+      <c r="C7" s="3" t="s">
         <v>28</v>
       </c>
       <c r="D7" s="4" t="s">
@@ -770,7 +772,7 @@
       <c r="E7" s="5"/>
     </row>
     <row r="8" spans="1:5" ht="80" x14ac:dyDescent="0.2">
-      <c r="A8" s="11" t="s">
+      <c r="A8" s="24" t="s">
         <v>12</v>
       </c>
       <c r="B8" s="3" t="s">
@@ -785,7 +787,7 @@
       <c r="E8" s="5"/>
     </row>
     <row r="9" spans="1:5" ht="64" x14ac:dyDescent="0.2">
-      <c r="A9" s="11" t="s">
+      <c r="A9" s="24" t="s">
         <v>11</v>
       </c>
       <c r="B9" s="3" t="s">
@@ -800,90 +802,99 @@
       <c r="E9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D10" s="18" t="s">
+      <c r="D10" s="21" t="s">
         <v>7</v>
       </c>
-      <c r="E10" s="21" t="s">
+      <c r="E10" s="22" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D11" s="18"/>
-      <c r="E11" s="22"/>
+      <c r="E11" s="12"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D12" s="19" t="s">
         <v>8</v>
       </c>
-      <c r="E12" s="23" t="s">
+      <c r="E12" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.2">
       <c r="D13" s="19"/>
-      <c r="E13" s="24"/>
+      <c r="E13" s="14"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="E14" s="25" t="s">
+      <c r="E14" s="15" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D15" s="20"/>
-      <c r="E15" s="26"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="16"/>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="E16" s="15"/>
+      <c r="E16" s="20"/>
     </row>
     <row r="17" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E17" s="15"/>
+      <c r="E17" s="20"/>
     </row>
     <row r="18" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E18" s="16"/>
+      <c r="E18" s="10"/>
     </row>
     <row r="19" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="E19" s="16"/>
+      <c r="E19" s="10"/>
     </row>
     <row r="20" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C20" s="13"/>
+      <c r="C20" s="7"/>
     </row>
     <row r="21" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C21" s="13"/>
+      <c r="C21" s="7"/>
     </row>
     <row r="22" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C22" s="14"/>
+      <c r="C22" s="8"/>
     </row>
     <row r="23" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C23" s="14"/>
+      <c r="C23" s="8"/>
     </row>
     <row r="24" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C24" s="17"/>
+      <c r="C24" s="9"/>
     </row>
     <row r="25" spans="3:5" x14ac:dyDescent="0.2">
-      <c r="C25" s="17"/>
+      <c r="C25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="D2:E2"/>
+    <mergeCell ref="D10:D11"/>
+    <mergeCell ref="D12:D13"/>
+    <mergeCell ref="E16:E17"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="D14:D15"/>
     <mergeCell ref="E10:E11"/>
     <mergeCell ref="E12:E13"/>
     <mergeCell ref="E14:E15"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="D2:E2"/>
-    <mergeCell ref="D10:D11"/>
-    <mergeCell ref="D12:D13"/>
-    <mergeCell ref="E16:E17"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" scale="77" orientation="landscape" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Dokument" ma:contentTypeID="0x01010047E1B4110D667F4BADC525742D5EE2E5" ma:contentTypeVersion="11" ma:contentTypeDescription="Ein neues Dokument erstellen." ma:contentTypeScope="" ma:versionID="d4242f0faca51ba845790f185672872f">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b989ebd0-cfbd-4347-a61d-09d2ec87900e" xmlns:ns3="26aae414-ca61-41d7-9f0a-f5a0a53751b8" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="d27d03a123c6c0eefdfdcad7d866e60f" ns2:_="" ns3:_="">
     <xsd:import namespace="b989ebd0-cfbd-4347-a61d-09d2ec87900e"/>
@@ -1078,15 +1089,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -1099,6 +1101,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C00B6F33-1652-4D35-BCCC-71D64DD37397}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -1117,14 +1127,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{015A24B1-25E6-4FDF-9F85-23E1FF82C0DE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DD56C91E-EFEF-46AC-A071-D7F993F6AB1F}">
   <ds:schemaRefs>
